--- a/SolidgroundUX devlog.xlsx
+++ b/SolidgroundUX devlog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Files\Development\Linux.sh\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Files\Development\Linux.sh\solidgroundux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5DD6E6-316F-4D8F-B821-47072E989873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C178C3B-8ED3-443E-B9F9-9ED11E8887E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18135" yWindow="3240" windowWidth="48255" windowHeight="31470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18135" yWindow="480" windowWidth="48255" windowHeight="31470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devlog" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
   <si>
     <t>ID</t>
   </si>
@@ -91,6 +91,42 @@
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t>SGUX-0002</t>
+  </si>
+  <si>
+    <t>Install procedure</t>
+  </si>
+  <si>
+    <t>Chicken and egg</t>
+  </si>
+  <si>
+    <t>On first install the sequence of events was murky at best</t>
+  </si>
+  <si>
+    <t>Changed code to ignore reccursive trees</t>
+  </si>
+  <si>
+    <t>Redefined, adapted INSTALL.md and documentation accordingly</t>
+  </si>
+  <si>
+    <t>SGUX-0003</t>
+  </si>
+  <si>
+    <t>MOTD</t>
+  </si>
+  <si>
+    <t>CR</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Add decent framework style motd</t>
+  </si>
+  <si>
+    <t>Adapted 90_solidgroundux</t>
   </si>
 </sst>
 </file>
@@ -442,18 +478,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="12" style="7" customWidth="1"/>
     <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="49.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -516,18 +553,65 @@
       <c r="I2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="J2" s="1" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
+      <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="D3" s="6"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="E3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="2">
+        <v>46186</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2">
+        <v>46189</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SolidgroundUX devlog.xlsx
+++ b/SolidgroundUX devlog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Files\Development\Linux.sh\solidgroundux\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C178C3B-8ED3-443E-B9F9-9ED11E8887E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F61A91-1372-49BD-A332-741944BB4CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18135" yWindow="480" windowWidth="48255" windowHeight="31470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -127,6 +127,24 @@
   </si>
   <si>
     <t>Adapted 90_solidgroundux</t>
+  </si>
+  <si>
+    <t>SGUX-0004</t>
+  </si>
+  <si>
+    <t>UI-Framework</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>Silent mode</t>
+  </si>
+  <si>
+    <t>Although very informative at designtime, the console logging can be somewhat verbose</t>
+  </si>
+  <si>
+    <t>Implemented new log levels, applied it oo he minimal UI section of the exe-template. Now able to run completely silent</t>
   </si>
 </sst>
 </file>
@@ -175,28 +193,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -478,139 +499,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="12" style="7" customWidth="1"/>
-    <col min="5" max="5" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="52.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="49.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" style="3" customWidth="1"/>
+    <col min="4" max="4" width="12" style="8" customWidth="1"/>
+    <col min="5" max="5" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="80.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="72.42578125" style="7" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="5">
         <v>46185</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="5">
         <v>46186</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="5">
         <v>46189</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="7" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="30">
+      <c r="A5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="5">
+        <v>46199</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/SolidgroundUX devlog.xlsx
+++ b/SolidgroundUX devlog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Files\Development\Linux.sh\solidgroundux\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37F61A91-1372-49BD-A332-741944BB4CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9ECDEE-97A3-46A3-8879-5991BC058AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18135" yWindow="480" windowWidth="48255" windowHeight="31470" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="32040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devlog" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
   <si>
     <t>ID</t>
   </si>
@@ -135,16 +138,58 @@
     <t>UI-Framework</t>
   </si>
   <si>
-    <t>HIGH</t>
-  </si>
-  <si>
     <t>Silent mode</t>
   </si>
   <si>
     <t>Although very informative at designtime, the console logging can be somewhat verbose</t>
   </si>
   <si>
-    <t>Implemented new log levels, applied it oo he minimal UI section of the exe-template. Now able to run completely silent</t>
+    <t>Info is outdated and doesn’t showcase UI capabilities</t>
+  </si>
+  <si>
+    <t>SGUX-0005</t>
+  </si>
+  <si>
+    <t>Bootstrap and template architecture</t>
+  </si>
+  <si>
+    <t>Implemented new log levels, applied it oo he minimal UI section of the exe-template. Now able to run completely silent. Silent is the default mode now</t>
+  </si>
+  <si>
+    <t>Move more boilerplate</t>
+  </si>
+  <si>
+    <t>Something needed changing in the bootstrap sequence, which meant having to change 12 scripts</t>
+  </si>
+  <si>
+    <t>Moved shared functions from template to separate library sgnd-exe-common.sh If desired functions can be overridden in the cloned script. If left alone, default bootstrapping process runs</t>
+  </si>
+  <si>
+    <t>SGUX-0006</t>
+  </si>
+  <si>
+    <t>ui-say.sh: sayprogress</t>
+  </si>
+  <si>
+    <t>Cursor not resetting right</t>
+  </si>
+  <si>
+    <t>When a progress bar is shown, the next progress is on the next line</t>
+  </si>
+  <si>
+    <t>Repaired cursor reset, now also working in multilevel mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGUX-0007 </t>
+  </si>
+  <si>
+    <t>framework-smoketest.sh</t>
+  </si>
+  <si>
+    <t>Extend testing</t>
+  </si>
+  <si>
+    <t>Added tests for say at ' trace'  loglevel, added progress test</t>
   </si>
 </sst>
 </file>
@@ -210,14 +255,14 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -499,19 +544,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="3" customWidth="1"/>
-    <col min="4" max="4" width="12" style="8" customWidth="1"/>
+    <col min="4" max="4" width="12" style="7" customWidth="1"/>
     <col min="5" max="5" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="80.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="72.42578125" style="7" customWidth="1"/>
+    <col min="10" max="10" width="72.42578125" style="6" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
@@ -572,10 +617,10 @@
       <c r="H2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -601,10 +646,10 @@
       <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="6" t="s">
         <v>23</v>
       </c>
     </row>
@@ -630,7 +675,10 @@
       <c r="H4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>29</v>
       </c>
     </row>
@@ -648,19 +696,100 @@
         <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G5" s="5">
         <v>46199</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="45">
+      <c r="A6" s="3" t="s">
         <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G6" s="5">
+        <v>46199</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="5">
+        <v>46206</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="5">
+        <v>46206</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/SolidgroundUX devlog.xlsx
+++ b/SolidgroundUX devlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\Mark\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D9ECDEE-97A3-46A3-8879-5991BC058AAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6B9B8E-9F14-4CCB-825C-02C7819C425F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="32040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17520" yWindow="3660" windowWidth="57600" windowHeight="23415" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devlog" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="70">
   <si>
     <t>ID</t>
   </si>
@@ -189,14 +189,74 @@
     <t>Extend testing</t>
   </si>
   <si>
-    <t>Added tests for say at ' trace'  loglevel, added progress test</t>
+    <t>Added tests for say at ' trace'  loglevel, added progress test, added All level</t>
+  </si>
+  <si>
+    <t>SGUX-0008</t>
+  </si>
+  <si>
+    <t>Clean installation issues</t>
+  </si>
+  <si>
+    <t>First install sequence of events</t>
+  </si>
+  <si>
+    <t>Several problems arose testing configuration scripts of cleanly installed VM's</t>
+  </si>
+  <si>
+    <t>Fixed sequence, default setting, some code cleanup</t>
+  </si>
+  <si>
+    <t>SGUX-0009</t>
+  </si>
+  <si>
+    <t>Progress bar</t>
+  </si>
+  <si>
+    <t>Progress bar not displayin glevels correctly</t>
+  </si>
+  <si>
+    <t>When multi level progress bars are used, the overwrite eachother</t>
+  </si>
+  <si>
+    <t>Fixed tightened begin and end cursor markers</t>
+  </si>
+  <si>
+    <t>SGUX-0010</t>
+  </si>
+  <si>
+    <t>Progress hindering….progress</t>
+  </si>
+  <si>
+    <t>Progressbar lower levels seems to be a performance killer, created an interval parameter, limitting the amount of File IO</t>
+  </si>
+  <si>
+    <t>Introduced an --interval parameter, is set base on job size</t>
+  </si>
+  <si>
+    <t>SGUX-0011</t>
+  </si>
+  <si>
+    <t>sgnd-bootstrap.sh</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>License accaptance not recorded</t>
+  </si>
+  <si>
+    <t>When I script runs, solidgroudn asks to confirm, the icense should be displayed</t>
+  </si>
+  <si>
+    <t>Some trouble ofver SolidgroundUX vs SolidGroundUX, the latter won, but not without a fight</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -216,6 +276,12 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -238,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -263,6 +329,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,7 +613,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.42578125" style="3" bestFit="1" customWidth="1"/>
@@ -553,7 +622,7 @@
     <col min="4" max="4" width="12" style="7" customWidth="1"/>
     <col min="5" max="5" width="5.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="31.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="80.85546875" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="72.42578125" style="6" customWidth="1"/>
@@ -579,7 +648,7 @@
       <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="9" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -718,6 +787,9 @@
       <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
+      <c r="C6" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="E6" s="3" t="s">
         <v>26</v>
       </c>
@@ -792,7 +864,125 @@
         <v>49</v>
       </c>
     </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="5">
+        <v>46210</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="5">
+        <v>46210</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="5">
+        <v>46211</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="30">
+      <c r="A12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="5">
+        <v>46210</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>